--- a/foto_2025_python_met_uitvragen.xlsx
+++ b/foto_2025_python_met_uitvragen.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'niet gekoppeld'!$A$1:$U$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'dubbele sleutels'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'onvolledige sleutels'!$A$1:$P$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'problemen varianten'!$A$1:$B$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'problemen varianten'!$A$1:$B$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5604,12 +5604,17 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>M Master of Arts Therapies</t>
+          <t>M Master of Music Therapy</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
           <t>260914_Kunstonderwijs_Uitvraag Codarts.xlsx</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>M Master Dance Movement Therapy</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9769,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>Art of Sound, Compositie, Hafabra Directie, Koordirectie, Orkestdirectie, Jazz compositie, Jazz contrabas, Jazz drums, Jazz basgitaar, Jazz fluit, Jazz gitaar, Jazz klarinet, Jazz piano, Jazz saxofoon, Jazz trombone, Jazz trompet, Jazz vibrafoon, Jazz viool, Jazz zang, Accordeon, Altviool, Bastrombone, Cello, Contrabas, Fagot, Fluit, Gitaar, Harp, Hobo, Klassiek Hoorn, Klarinet, Piano, Saxofoon, Slagwerk, Trombone, Trompet, Tuba, Viool, Barok altviool, Barok cello, Barok fagot, Barok harp, Barok hobo, Barok trombone, Barok viool, Blokfluit, Klavecimbel, Cornetto, Fortepiano, Historische klarinet, Luit/Theorbe, Natuurhoorn, Natuurtrompet, Orgel, Traverso, Viola da Gamba, Violone, Sonologie, Theorie der muziek, Zang Klassieke Muziek, Zang Oude Muziek</t>
+          <t>Art of Sound, Compositie, Directie,  Jazz, Klassiek, Sonologie, Theorie der muziek, Oude Muziek</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
@@ -10209,7 +10214,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>Art of Sound, ArtScience, Compositie, Hafabra Directie, Koordirectie, Nationale Master Orkestdirectie, Jazz compositie, Jazz contrabas, Jazz drums, Jazz basgitaar, Jazz fluit, Jazz gitaar, Jazz klarinet, Jazz piano, Jazz saxofoon, Jazz theorie der muziek, Jazz trombone, Jazz trompet, Jazz vibrafoon, Jazz vibrafoon, Jazz viool, Jazz zang, Accordeon, Altviool, Bastrombone, Bastrombone, Cello, Contrabas, European Chamber Music Master (ECMAster), Fagot, Fluit, Gitaar, Harp, Hobo, Klassiek hoorn, Klarinet, Piano, Saxofoon, Slagwerk, Trombone, Trompet, Tuba, Viool, The Musician Educator, Muziekeducatie, Muziekeducatie volgens het Kodály concept, New Audiences and Innovative Practice, Barok altviool, Barok cello, Barok fagot, Barok harp, Barok hobo, Barok trombone, Barok viool, Basso Continuo voor Klavecimbel, Blokfluit, Klavecimbel, Cornetto, European Master of Early Music, Fortepiano, Historische toetsinstrumenten, Historische klarinet, Luit/Theorbe, Natuurhoorn, Natuurtrompet, Orgel, Traverso, Viola da Gamba, Violone, Theorie der Muziek, Theorie der Oude Muziek, Zang Klassieke Muziek, Zang Oude Muziek, klassieke muziek, jazz, oude muziek, zang, directie, compositie, art of sound, sonologie, theorie der muziek, European Chamber Music Master (ECMAster), European Master of Early Music (EMEM), ArtScience, The Musician Education (TME), Music Education according to the Kodaly Concept, New Audiences and Innovative Practice (NAIP)</t>
+          <t>Art of Sound, ArtScience, Compositie, Directie, Jazz, European Chamber Music Master, Klassiek, The Musician Educator, Muziekeducatie, New Audiences and Innovative Practice, European Master of Early Music, Theorie der Muziek, Oude Muziek, New Audiences and Innovative Practice</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -11678,11 +11683,6 @@
       <c r="P161" t="n">
         <v>21.48</v>
       </c>
-      <c r="Q161" t="inlineStr">
-        <is>
-          <t>nee</t>
-        </is>
-      </c>
       <c r="S161" t="inlineStr">
         <is>
           <t>B Docent Theater</t>
@@ -11753,11 +11753,6 @@
       <c r="P162" t="n">
         <v>20.76</v>
       </c>
-      <c r="Q162" t="inlineStr">
-        <is>
-          <t>nee</t>
-        </is>
-      </c>
       <c r="S162" t="inlineStr">
         <is>
           <t>B Docent Beeldende Kunst en Vormgeving</t>
@@ -11875,7 +11870,7 @@
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>B Interior Design</t>
+          <t>B Vormgeving</t>
         </is>
       </c>
       <c r="T164" t="inlineStr">
@@ -12880,13 +12875,13 @@
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="43" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -13024,7 +13019,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>B Popular Culture International</t>
+          <t>B Popular Culture</t>
         </is>
       </c>
     </row>
@@ -13135,7 +13130,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>B Audiovisuele vormgeving</t>
+          <t>B Illustration</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>B Animation</t>
         </is>
       </c>
     </row>
@@ -13263,7 +13263,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>B Graphic and interaction design</t>
+          <t>B Grafisch ontwerpen</t>
         </is>
       </c>
     </row>
@@ -13815,7 +13815,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>B Dirigent HaFaBra</t>
+          <t>B Dirigent</t>
         </is>
       </c>
     </row>
@@ -13855,7 +13855,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>B Dirigent Koor</t>
+          <t>B Dirigent</t>
         </is>
       </c>
     </row>
@@ -13896,7 +13896,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>B Compositie en muziekproductie</t>
+          <t>B Compositie</t>
         </is>
       </c>
     </row>
@@ -15487,7 +15487,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>B Image and Media Technology</t>
+          <t>B Media</t>
         </is>
       </c>
     </row>
@@ -15538,7 +15538,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>B Graphic Design</t>
+          <t>B Grafisch ontwerpen</t>
         </is>
       </c>
     </row>
@@ -16067,7 +16067,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>B Historical Performance Practice</t>
+          <t>B Muziekgeschiedenis</t>
         </is>
       </c>
     </row>
@@ -16176,7 +16176,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>B Musician 3.0</t>
+          <t>B Muziek</t>
         </is>
       </c>
     </row>
@@ -16220,7 +16220,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>B The Netherlands Carillon School</t>
+          <t>B Klassiek</t>
         </is>
       </c>
     </row>
@@ -16276,7 +16276,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>B Composition Elektronic Music</t>
+          <t>B Compositie</t>
         </is>
       </c>
     </row>
@@ -16332,7 +16332,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>B Composition for the Media</t>
+          <t>B Compositie</t>
         </is>
       </c>
     </row>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>B Music Design for Games and Interaction</t>
+          <t>B Muziek ontwerp</t>
         </is>
       </c>
     </row>
@@ -16444,7 +16444,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>B Composition and Music Production</t>
+          <t>B Compositie</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>B Muziekproductie</t>
         </is>
       </c>
     </row>
@@ -16597,7 +16602,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>B Acting</t>
+          <t>B Acteur</t>
         </is>
       </c>
     </row>
@@ -16641,7 +16646,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>B Interactive Performance Design</t>
+          <t>B Scenografie</t>
         </is>
       </c>
     </row>
@@ -16729,7 +16734,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>B Theatre Design</t>
+          <t>B Scenografie</t>
         </is>
       </c>
     </row>
@@ -16749,7 +16754,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">M Master of Arts in Fine Arts and Design </t>
+          <t xml:space="preserve">M Master of Arts in Fine Art and Design </t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -16793,7 +16798,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">M Master of Arts in Fine Arts and Design </t>
+          <t xml:space="preserve">M Master of Arts in Fine Art and Design </t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -18367,7 +18372,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>B Klasiek</t>
+          <t>B Klassiek</t>
         </is>
       </c>
     </row>
@@ -18758,7 +18763,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>B SNDO (school voor nieuwe dansontwikkeling)</t>
+          <t>B Choreografie</t>
         </is>
       </c>
     </row>
@@ -18806,7 +18811,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve"> B ECD (expanded contemporary dance)</t>
+          <t xml:space="preserve"> B Dans</t>
         </is>
       </c>
     </row>
@@ -18902,7 +18907,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>B ATKA (Amsterdamse Toneelschool en Kleinkunstacademie)</t>
+          <t>B Acteur</t>
         </is>
       </c>
     </row>
@@ -19137,7 +19142,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>B Opleiding Productie Podiumkunsten</t>
+          <t>B Productie Podiumkunsten</t>
         </is>
       </c>
     </row>
@@ -21937,7 +21942,12 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>B Illustrative &amp; Animated Storytelling</t>
+          <t>B Illustartion</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>B Animation</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -22014,7 +22024,12 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>B New Design &amp; Attitudes</t>
+          <t>B Grafisch ontwerpen</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>B Ruimtelijk ontwerpen</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -22067,7 +22082,12 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>B Photography, Film &amp; The Digital</t>
+          <t>B Photography</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>B Film</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -22121,7 +22141,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>B Illustrative &amp; Animated Storytelling</t>
+          <t>B Illustartion</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>B Animation</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -22198,7 +22223,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>B New Design &amp; Attitudes</t>
+          <t>B Grafisch ontwerpen</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>B Ruimtelijk ontwerpen</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -22250,7 +22280,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Ma Social Design</t>
+          <t>M Design</t>
         </is>
       </c>
     </row>
@@ -22296,7 +22326,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Ma Contextual Design</t>
+          <t>M Design</t>
         </is>
       </c>
     </row>
@@ -22345,7 +22375,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>Ma Information Design</t>
+          <t>M Design</t>
         </is>
       </c>
     </row>
@@ -22391,7 +22421,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Ma Geo Design</t>
+          <t>M Design</t>
         </is>
       </c>
     </row>
@@ -22436,7 +22466,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Ma Critical Inquiry Lab</t>
+          <t>M Critical Studies</t>
         </is>
       </c>
     </row>
@@ -22732,7 +22762,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>B Pabo Kunsten</t>
+          <t>B Docent Beeldende kunst</t>
         </is>
       </c>
     </row>
@@ -22768,7 +22798,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>B Pabo Kunsten</t>
+          <t>B Docent Muziek</t>
         </is>
       </c>
     </row>
@@ -22788,7 +22818,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>DOGtime</t>
+          <t>B Beeldende Kunst en Vormgeving</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -22812,8 +22842,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">B DOGtime Basic Year 
-</t>
+          <t>B DOGtime</t>
         </is>
       </c>
     </row>
@@ -22833,7 +22862,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>DOGtime</t>
+          <t>B Beeldende Kunst en Vormgeving</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -22857,8 +22886,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">B DOGtime Unstable Media 
-</t>
+          <t>B DOGtime</t>
         </is>
       </c>
     </row>
@@ -22878,7 +22906,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>DOGtime</t>
+          <t>B Beeldende Kunst en Vormgeving</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -22901,7 +22929,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>B DOGtime Expanded Painting</t>
+          <t>B DOGtime</t>
         </is>
       </c>
     </row>
@@ -23030,7 +23058,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>B OntwerpLAB</t>
+          <t>B Product design</t>
         </is>
       </c>
     </row>
@@ -23159,7 +23187,7 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>B Grafisch ontwerp</t>
+          <t>B Grafisch ontwerpen</t>
         </is>
       </c>
     </row>
@@ -23245,7 +23273,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>B Sieraden - Lichamen verbinden</t>
+          <t>B Sieraden</t>
         </is>
       </c>
     </row>
@@ -23288,7 +23316,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>B Fotografie</t>
+          <t>B Photography</t>
         </is>
       </c>
     </row>
@@ -23331,7 +23359,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>B De afdeling Groot Glas</t>
+          <t>B Glas</t>
         </is>
       </c>
     </row>
@@ -23374,7 +23402,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>B TXT (Textiel en Tekst)</t>
+          <t>B Textiel</t>
         </is>
       </c>
     </row>
@@ -23417,7 +23445,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>B VAV</t>
+          <t>B Film</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>B Media</t>
         </is>
       </c>
     </row>
@@ -23465,7 +23498,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">M Fine Art  
+          <t xml:space="preserve">M Fine Art
 </t>
         </is>
       </c>
@@ -23634,7 +23667,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>- Monstrous Futurities (graduation 2027)</t>
+          <t>Monstrous Futurities (graduation 2027)</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -23682,7 +23715,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>- Phantom Scores (graduation 2028)</t>
+          <t>Phantom Scores (graduation 2028)</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -26118,7 +26151,7 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>B Fotografie</t>
+          <t>B Photography</t>
         </is>
       </c>
     </row>
@@ -26166,7 +26199,7 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>B Grafisch Ontwerpen</t>
+          <t>B Grafisch ontwerpen</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26247,7 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>B Interactive Media Design</t>
+          <t>B Media</t>
         </is>
       </c>
     </row>
@@ -26262,7 +26295,7 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>B Interieurarchitectuur en meubelontwerpen</t>
+          <t>B Interieurarchitectuur</t>
         </is>
       </c>
     </row>
@@ -26310,7 +26343,12 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>B Textiel en Mode</t>
+          <t>B Textiel</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>B Mode</t>
         </is>
       </c>
     </row>
@@ -26355,7 +26393,7 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>B Docent Muziek verkort</t>
+          <t>B Docent Muziek</t>
         </is>
       </c>
     </row>
@@ -29026,52 +29064,19 @@
         </is>
       </c>
       <c r="C376" t="n">
-        <v>49105</v>
+        <v>49114</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>M Opera</t>
+          <t>M Master of Arts in Fine Art and Design</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Opera</t>
-        </is>
-      </c>
-      <c r="G376" t="n">
-        <v>6</v>
-      </c>
-      <c r="I376" t="inlineStr">
-        <is>
-          <t>M Opera</t>
-        </is>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>Hogeschool der Kunsten Den Haag</t>
-        </is>
-      </c>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>Uitvraag Hogeschool der Kunsten Den Haag - HdK-KC-KA 280926.xlsx</t>
-        </is>
-      </c>
-      <c r="C377" t="n">
-        <v>49114</v>
-      </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>M Master of Arts in Fine Art and Design</t>
-        </is>
-      </c>
-      <c r="E377" t="inlineStr">
-        <is>
           <t>Artistic Research</t>
         </is>
       </c>
-      <c r="F377" t="inlineStr">
+      <c r="F376" t="inlineStr">
         <is>
           <t>• Conceptuele diepgang en visuele taal rond identiteit, duurzaamheid, technologie en samenleving
 • (Innovatieve) materiaalkennis en theoretische vakken per discipline
@@ -29081,45 +29086,45 @@
 • 2-jarige opleiding</t>
         </is>
       </c>
-      <c r="G377" t="n">
+      <c r="G376" t="n">
         <v>24</v>
       </c>
-      <c r="H377" t="inlineStr">
+      <c r="H376" t="inlineStr">
         <is>
           <t>Nee</t>
         </is>
       </c>
-      <c r="I377" t="inlineStr">
+      <c r="I376" t="inlineStr">
         <is>
           <t>M Artistic Research</t>
         </is>
       </c>
     </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
+    <row r="377">
+      <c r="A377" t="inlineStr">
         <is>
           <t>Hogeschool der Kunsten Den Haag</t>
         </is>
       </c>
-      <c r="B378" t="inlineStr">
+      <c r="B377" t="inlineStr">
         <is>
           <t>Uitvraag Hogeschool der Kunsten Den Haag - HdK-KC-KA 280926.xlsx</t>
         </is>
       </c>
-      <c r="C378" t="n">
+      <c r="C377" t="n">
         <v>49114</v>
       </c>
-      <c r="D378" t="inlineStr">
+      <c r="D377" t="inlineStr">
         <is>
           <t>M Master of Arts in Fine Art and Design</t>
         </is>
       </c>
-      <c r="E378" t="inlineStr">
+      <c r="E377" t="inlineStr">
         <is>
           <t>Industrial Design</t>
         </is>
       </c>
-      <c r="F378" t="inlineStr">
+      <c r="F377" t="inlineStr">
         <is>
           <t>• Conceptuele diepgang en visuele taal rond identiteit, duurzaamheid, technologie en samenleving
 • (Innovatieve) materiaalkennis en theoretische vakken per discipline
@@ -29129,45 +29134,45 @@
 • 2-jarige opleiding</t>
         </is>
       </c>
-      <c r="G378" t="n">
+      <c r="G377" t="n">
         <v>22</v>
       </c>
-      <c r="H378" t="inlineStr">
+      <c r="H377" t="inlineStr">
         <is>
           <t>Nee</t>
         </is>
       </c>
-      <c r="I378" t="inlineStr">
+      <c r="I377" t="inlineStr">
         <is>
           <t>M Industrial Design</t>
         </is>
       </c>
     </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
+    <row r="378">
+      <c r="A378" t="inlineStr">
         <is>
           <t>Hogeschool der Kunsten Den Haag</t>
         </is>
       </c>
-      <c r="B379" t="inlineStr">
+      <c r="B378" t="inlineStr">
         <is>
           <t>Uitvraag Hogeschool der Kunsten Den Haag - HdK-KC-KA 280926.xlsx</t>
         </is>
       </c>
-      <c r="C379" t="n">
+      <c r="C378" t="n">
         <v>49114</v>
       </c>
-      <c r="D379" t="inlineStr">
+      <c r="D378" t="inlineStr">
         <is>
           <t>M Master of Arts in Fine Art and Design</t>
         </is>
       </c>
-      <c r="E379" t="inlineStr">
+      <c r="E378" t="inlineStr">
         <is>
           <t>Non-Linear Narrative</t>
         </is>
       </c>
-      <c r="F379" t="inlineStr">
+      <c r="F378" t="inlineStr">
         <is>
           <t>• Conceptuele diepgang en visuele taal rond identiteit, duurzaamheid, technologie en samenleving
 • (Innovatieve) materiaalkennis en theoretische vakken per discipline
@@ -29177,45 +29182,45 @@
 • 2-jarige opleiding</t>
         </is>
       </c>
-      <c r="G379" t="n">
+      <c r="G378" t="n">
         <v>20</v>
       </c>
-      <c r="H379" t="inlineStr">
+      <c r="H378" t="inlineStr">
         <is>
           <t>Nee</t>
         </is>
       </c>
-      <c r="I379" t="inlineStr">
+      <c r="I378" t="inlineStr">
         <is>
           <t>M Non-Linear Narrative</t>
         </is>
       </c>
     </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
+    <row r="379">
+      <c r="A379" t="inlineStr">
         <is>
           <t>Hogeschool der Kunsten Den Haag</t>
         </is>
       </c>
-      <c r="B380" t="inlineStr">
+      <c r="B379" t="inlineStr">
         <is>
           <t>Uitvraag Hogeschool der Kunsten Den Haag - HdK-KC-KA 280926.xlsx</t>
         </is>
       </c>
-      <c r="C380" t="n">
+      <c r="C379" t="n">
         <v>49114</v>
       </c>
-      <c r="D380" t="inlineStr">
+      <c r="D379" t="inlineStr">
         <is>
           <t>M Master of Arts in Fine Art and Design</t>
         </is>
       </c>
-      <c r="E380" t="inlineStr">
+      <c r="E379" t="inlineStr">
         <is>
           <t>Photography &amp; Society</t>
         </is>
       </c>
-      <c r="F380" t="inlineStr">
+      <c r="F379" t="inlineStr">
         <is>
           <t>• Conceptuele diepgang en visuele taal rond identiteit, duurzaamheid, technologie en samenleving
 • (Innovatieve) materiaalkennis en theoretische vakken per discipline
@@ -29225,17 +29230,60 @@
 • 2-jarige opleiding</t>
         </is>
       </c>
+      <c r="G379" t="n">
+        <v>29</v>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>M Photography &amp; Society</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Saxion Hogeschool</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Uitvraag Saxion.xlsx</t>
+        </is>
+      </c>
+      <c r="C380" t="n">
+        <v>39210</v>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>B Interior Design</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>B Interior Design</t>
+        </is>
+      </c>
       <c r="G380" t="n">
-        <v>29</v>
+        <v>705</v>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t xml:space="preserve">Interieur ontwerp, ruimtelijk vormgeven. Onze opleiding heeft een uniek ISAT code. en is in die zin een een unieke op leiding (Zie ook vraag 7) Verwante opleidingen (maar dus beslist niet het zelfde) zijn alle opleidingen aan de kunstacademies waarbij Ruimtelijk onterp, interieur etc. centraal staat. Zoals de HKU en Interieur ontwerp bij Artez </t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>M Photography &amp; Society</t>
+          <t>B Interieurarchitectuur</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>B Ruimtelijk ontwerpen</t>
         </is>
       </c>
     </row>
@@ -29481,7 +29529,7 @@
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>B Regisseur</t>
+          <t>B Regie</t>
         </is>
       </c>
     </row>
@@ -29629,7 +29677,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -29649,7 +29697,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -30236,7 +30284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -30279,20 +30327,8 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Uitvraag Saxion.xlsx</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Tabblad Varianten ontbreekt</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:B4"/>
+  <autoFilter ref="A1:B3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -30451,13 +30487,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A281A89-AD5E-4840-B7C5-2A02508A2105}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AFB0FF9-1300-4849-9D8D-7F86930B94AC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E518B1C9-F6B0-4401-81F1-120C188516D0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82302493-68D9-4D05-BD74-DBDF78C3434F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{651BB7B6-F00E-41D5-8631-D2FAF8E6B36F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33224E81-07BB-4D18-A0D5-F33BFDE9FE46}"/>
 </file>